--- a/backend/data.xlsx
+++ b/backend/data.xlsx
@@ -1,31 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCF50FA-54A5-41EE-A899-117A36A89833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>company</t>
+  </si>
+  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Phone</t>
   </si>
   <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>Project Budget</t>
+  </si>
+  <si>
+    <t>Project Description</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
     <t>chinna</t>
   </si>
   <si>
@@ -44,57 +58,102 @@
     <t>iojosndjnn</t>
   </si>
   <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>Project Description</t>
-  </si>
-  <si>
-    <t>Project Budget</t>
-  </si>
-  <si>
-    <t>Project Type</t>
+    <t>mohana</t>
+  </si>
+  <si>
+    <t>Fly Towards Digital Innovation</t>
+  </si>
+  <si>
+    <t>mohanam@gmail.com</t>
+  </si>
+  <si>
+    <t>9876543021</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>assdfghhkk</t>
+  </si>
+  <si>
+    <t>asdfghjkloiu</t>
+  </si>
+  <si>
+    <t>1773814744762-Brain_Tumor_Report_3.pdf</t>
+  </si>
+  <si>
+    <t>priya</t>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
+    <t>priya@gmail.com</t>
+  </si>
+  <si>
+    <t>7890654321</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>njikolmnop</t>
+  </si>
+  <si>
+    <t>1773815423641-Brain_Tumor_Report_2.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF334155"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FF334155"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color rgb="FF0D0D0D"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <family val="1"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,14 +176,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,9 +523,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="28.5546875" customWidth="1"/>
@@ -473,56 +533,135 @@
     <col min="5" max="5" width="23.44140625" customWidth="1"/>
     <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="32.77734375" customWidth="1"/>
+    <col min="8" max="8" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.6" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>10</v>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/backend/data.xlsx
+++ b/backend/data.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC53549-B699-45B3-BF0A-464653A975C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Phone</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>Phone Number</t>
   </si>
   <si>
     <t>Project Type</t>
@@ -37,123 +38,51 @@
     <t>Project Description</t>
   </si>
   <si>
-    <t>Document</t>
-  </si>
-  <si>
-    <t>chinna</t>
-  </si>
-  <si>
-    <t>c@gmail.com</t>
-  </si>
-  <si>
-    <t>+91 9977454123</t>
+    <t>Uploaded Document</t>
+  </si>
+  <si>
+    <t>sugii</t>
+  </si>
+  <si>
+    <t>cfgh</t>
+  </si>
+  <si>
+    <t>sugi@gmail.com</t>
+  </si>
+  <si>
+    <t>6789054321</t>
   </si>
   <si>
     <t>mobile</t>
   </si>
   <si>
-    <t>1000-20000</t>
-  </si>
-  <si>
-    <t>iojosndjnn</t>
-  </si>
-  <si>
-    <t>mohana</t>
-  </si>
-  <si>
-    <t>Fly Towards Digital Innovation</t>
-  </si>
-  <si>
-    <t>mohanam@gmail.com</t>
-  </si>
-  <si>
-    <t>9876543021</t>
-  </si>
-  <si>
-    <t>web</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>assdfghhkk</t>
-  </si>
-  <si>
-    <t>asdfghjkloiu</t>
-  </si>
-  <si>
-    <t>1773814744762-Brain_Tumor_Report_3.pdf</t>
-  </si>
-  <si>
-    <t>priya</t>
-  </si>
-  <si>
-    <t>ABCD</t>
-  </si>
-  <si>
-    <t>priya@gmail.com</t>
-  </si>
-  <si>
-    <t>7890654321</t>
-  </si>
-  <si>
-    <t>design</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>njikolmnop</t>
-  </si>
-  <si>
-    <t>1773815423641-Brain_Tumor_Report_2.pdf</t>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>qwertyuiop</t>
+  </si>
+  <si>
+    <t>Open File</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF334155"/>
-      <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <color rgb="FF0D0D0D"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="1"/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,15 +105,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,145 +446,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="32.77734375" customWidth="1"/>
-    <col min="8" max="8" width="37.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H2" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/data.xlsx
+++ b/backend/data.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC53549-B699-45B3-BF0A-464653A975C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>Full Name</t>
   </si>
@@ -63,26 +62,59 @@
   </si>
   <si>
     <t>Open File</t>
+  </si>
+  <si>
+    <t>chinna</t>
+  </si>
+  <si>
+    <t>a@company.com</t>
+  </si>
+  <si>
+    <t>+91 9632587411</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>1000-2000</t>
+  </si>
+  <si>
+    <t>dnrkjjng</t>
+  </si>
+  <si>
+    <t>raja</t>
+  </si>
+  <si>
+    <t>r@company.com</t>
+  </si>
+  <si>
+    <t>7894561234</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>ijninnd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -446,9 +478,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
@@ -460,7 +492,7 @@
     <col min="8" max="8" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,14 +541,68 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>